--- a/artfynd/A 51902-2023 artfynd.xlsx
+++ b/artfynd/A 51902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119150262</v>
+        <v>119150194</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486232</v>
+        <v>485965</v>
       </c>
       <c r="R2" t="n">
-        <v>6817200</v>
+        <v>6817281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,18 +748,12 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119150281</v>
+        <v>119150195</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486003</v>
+        <v>485994</v>
       </c>
       <c r="R3" t="n">
-        <v>6817262</v>
+        <v>6817274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119150316</v>
+        <v>119150196</v>
       </c>
       <c r="B4" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486041</v>
+        <v>485978</v>
       </c>
       <c r="R4" t="n">
-        <v>6817122</v>
+        <v>6817240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119150332</v>
+        <v>119150197</v>
       </c>
       <c r="B5" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486120</v>
+        <v>486004</v>
       </c>
       <c r="R5" t="n">
-        <v>6817245</v>
+        <v>6817124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119150235</v>
+        <v>119150198</v>
       </c>
       <c r="B6" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485963</v>
+        <v>486047</v>
       </c>
       <c r="R6" t="n">
-        <v>6817028</v>
+        <v>6816930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119150217</v>
+        <v>119150199</v>
       </c>
       <c r="B7" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485996</v>
+        <v>486048</v>
       </c>
       <c r="R7" t="n">
-        <v>6817083</v>
+        <v>6816957</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119150202</v>
+        <v>119150200</v>
       </c>
       <c r="B8" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486042</v>
+        <v>486044</v>
       </c>
       <c r="R8" t="n">
-        <v>6817070</v>
+        <v>6816955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119150353</v>
+        <v>119150201</v>
       </c>
       <c r="B9" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486009</v>
+        <v>486026</v>
       </c>
       <c r="R9" t="n">
-        <v>6817379</v>
+        <v>6817016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119150200</v>
+        <v>119150202</v>
       </c>
       <c r="B10" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486044</v>
+        <v>486042</v>
       </c>
       <c r="R10" t="n">
-        <v>6816955</v>
+        <v>6817070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119150285</v>
+        <v>119150203</v>
       </c>
       <c r="B11" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485983</v>
+        <v>486021</v>
       </c>
       <c r="R11" t="n">
-        <v>6817246</v>
+        <v>6817092</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119150349</v>
+        <v>119150204</v>
       </c>
       <c r="B12" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486057</v>
+        <v>486018</v>
       </c>
       <c r="R12" t="n">
-        <v>6817342</v>
+        <v>6817110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119150283</v>
+        <v>119150205</v>
       </c>
       <c r="B13" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486010</v>
+        <v>486049</v>
       </c>
       <c r="R13" t="n">
-        <v>6817248</v>
+        <v>6817096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,59 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119150266</v>
+        <v>119150206</v>
       </c>
       <c r="B14" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486120</v>
+        <v>486072</v>
       </c>
       <c r="R14" t="n">
-        <v>6817186</v>
+        <v>6817320</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119150327</v>
+        <v>119150207</v>
       </c>
       <c r="B15" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486173</v>
+        <v>486080</v>
       </c>
       <c r="R15" t="n">
-        <v>6817207</v>
+        <v>6817326</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,12 +2036,7 @@
         <v>119150208</v>
       </c>
       <c r="B16" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119150223</v>
+        <v>119150359</v>
       </c>
       <c r="B17" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485963</v>
+        <v>485978</v>
       </c>
       <c r="R17" t="n">
-        <v>6817028</v>
+        <v>6817236</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119150224</v>
+        <v>119150360</v>
       </c>
       <c r="B18" t="n">
-        <v>79606</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486273</v>
+        <v>485968</v>
       </c>
       <c r="R18" t="n">
-        <v>6817148</v>
+        <v>6817191</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119150228</v>
+        <v>119150361</v>
       </c>
       <c r="B19" t="n">
-        <v>91830</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,43 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486032</v>
+        <v>486064</v>
       </c>
       <c r="R19" t="n">
-        <v>6817084</v>
+        <v>6817046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,50 +2421,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119150333</v>
+        <v>119150231</v>
       </c>
       <c r="B20" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486124</v>
+        <v>485997</v>
       </c>
       <c r="R20" t="n">
-        <v>6817261</v>
+        <v>6817109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,12 +2497,18 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2653,37 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119150287</v>
+        <v>119150273</v>
       </c>
       <c r="B21" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486004</v>
+        <v>486037</v>
       </c>
       <c r="R21" t="n">
-        <v>6817124</v>
+        <v>6817075</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,15 +2624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119150189</v>
+        <v>119150223</v>
       </c>
       <c r="B22" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,21 +2635,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485979</v>
+        <v>485963</v>
       </c>
       <c r="R22" t="n">
-        <v>6816957</v>
+        <v>6817028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,37 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119150273</v>
+        <v>119150224</v>
       </c>
       <c r="B23" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486037</v>
+        <v>486273</v>
       </c>
       <c r="R23" t="n">
-        <v>6817075</v>
+        <v>6817148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,37 +2818,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119150199</v>
+        <v>119150243</v>
       </c>
       <c r="B24" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>2387</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2853,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486048</v>
+        <v>486026</v>
       </c>
       <c r="R24" t="n">
-        <v>6816957</v>
+        <v>6816986</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,15 +2915,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119150292</v>
+        <v>119150228</v>
       </c>
       <c r="B25" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,34 +2926,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485924</v>
+        <v>486032</v>
       </c>
       <c r="R25" t="n">
-        <v>6817014</v>
+        <v>6817084</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,15 +3021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119150305</v>
+        <v>119150358</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,34 +3032,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486016</v>
+        <v>486031</v>
       </c>
       <c r="R26" t="n">
-        <v>6816990</v>
+        <v>6817090</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,15 +3127,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119150350</v>
+        <v>119150211</v>
       </c>
       <c r="B27" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3281,21 +3138,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486051</v>
+        <v>486007</v>
       </c>
       <c r="R27" t="n">
-        <v>6817353</v>
+        <v>6817113</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3367,37 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119150304</v>
+        <v>119150213</v>
       </c>
       <c r="B28" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3407,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486044</v>
+        <v>486259</v>
       </c>
       <c r="R28" t="n">
-        <v>6816955</v>
+        <v>6817166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,59 +3321,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119150251</v>
+        <v>119150214</v>
       </c>
       <c r="B29" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486127</v>
+        <v>485994</v>
       </c>
       <c r="R29" t="n">
-        <v>6817270</v>
+        <v>6817373</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3580,15 +3418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119150253</v>
+        <v>119150276</v>
       </c>
       <c r="B30" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,43 +3429,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486122</v>
+        <v>485970</v>
       </c>
       <c r="R30" t="n">
-        <v>6817177</v>
+        <v>6817296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3691,37 +3515,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119150236</v>
+        <v>119150277</v>
       </c>
       <c r="B31" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3731,10 +3550,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486274</v>
+        <v>485966</v>
       </c>
       <c r="R31" t="n">
-        <v>6817146</v>
+        <v>6817281</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,37 +3612,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119150237</v>
+        <v>119150278</v>
       </c>
       <c r="B32" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3833,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486273</v>
+        <v>485979</v>
       </c>
       <c r="R32" t="n">
-        <v>6817146</v>
+        <v>6817277</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,37 +3709,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119150221</v>
+        <v>119150279</v>
       </c>
       <c r="B33" t="n">
-        <v>97926</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3935,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485997</v>
+        <v>485985</v>
       </c>
       <c r="R33" t="n">
-        <v>6816970</v>
+        <v>6817278</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,15 +3806,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119150261</v>
+        <v>119150280</v>
       </c>
       <c r="B34" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4013,43 +3817,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486161</v>
+        <v>485993</v>
       </c>
       <c r="R34" t="n">
-        <v>6817238</v>
+        <v>6817274</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4108,15 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119150267</v>
+        <v>119150281</v>
       </c>
       <c r="B35" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4124,43 +3914,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485912</v>
+        <v>486003</v>
       </c>
       <c r="R35" t="n">
-        <v>6816984</v>
+        <v>6817262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4219,15 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119150254</v>
+        <v>119150282</v>
       </c>
       <c r="B36" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4235,43 +4011,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486174</v>
+        <v>486007</v>
       </c>
       <c r="R36" t="n">
-        <v>6817201</v>
+        <v>6817254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4330,19 +4097,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119150291</v>
+        <v>119150283</v>
       </c>
       <c r="B37" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4370,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485953</v>
+        <v>486010</v>
       </c>
       <c r="R37" t="n">
-        <v>6817006</v>
+        <v>6817248</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4432,19 +4194,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119150322</v>
+        <v>119150284</v>
       </c>
       <c r="B38" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4472,10 +4229,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486264</v>
+        <v>485994</v>
       </c>
       <c r="R38" t="n">
-        <v>6817132</v>
+        <v>6817252</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4534,37 +4291,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119150210</v>
+        <v>119150285</v>
       </c>
       <c r="B39" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4574,10 +4326,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485992</v>
+        <v>485983</v>
       </c>
       <c r="R39" t="n">
-        <v>6817278</v>
+        <v>6817246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4636,19 +4388,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119150338</v>
+        <v>119150286</v>
       </c>
       <c r="B40" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4676,10 +4423,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486090</v>
+        <v>485981</v>
       </c>
       <c r="R40" t="n">
-        <v>6817306</v>
+        <v>6817231</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4738,19 +4485,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119150308</v>
+        <v>119150287</v>
       </c>
       <c r="B41" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4778,10 +4520,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486025</v>
+        <v>486004</v>
       </c>
       <c r="R41" t="n">
-        <v>6817022</v>
+        <v>6817124</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,15 +4582,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119150252</v>
+        <v>119150288</v>
       </c>
       <c r="B42" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4856,43 +4593,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486019</v>
+        <v>485994</v>
       </c>
       <c r="R42" t="n">
-        <v>6816965</v>
+        <v>6817085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,37 +4679,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119150201</v>
+        <v>119150289</v>
       </c>
       <c r="B43" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4991,10 +4714,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486026</v>
+        <v>485978</v>
       </c>
       <c r="R43" t="n">
-        <v>6817016</v>
+        <v>6817031</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5053,58 +4776,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119150218</v>
+        <v>119150290</v>
       </c>
       <c r="B44" t="n">
-        <v>97926</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486005</v>
+        <v>485975</v>
       </c>
       <c r="R44" t="n">
-        <v>6816970</v>
+        <v>6817009</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5145,7 +4855,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5164,15 +4873,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119150269</v>
+        <v>119150291</v>
       </c>
       <c r="B45" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,43 +4884,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486231</v>
+        <v>485953</v>
       </c>
       <c r="R45" t="n">
-        <v>6817154</v>
+        <v>6817006</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5275,19 +4970,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119150347</v>
+        <v>119150292</v>
       </c>
       <c r="B46" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5315,10 +5005,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486061</v>
+        <v>485924</v>
       </c>
       <c r="R46" t="n">
-        <v>6817331</v>
+        <v>6817014</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5377,19 +5067,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119150279</v>
+        <v>119150293</v>
       </c>
       <c r="B47" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5417,10 +5102,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485985</v>
+        <v>485956</v>
       </c>
       <c r="R47" t="n">
-        <v>6817278</v>
+        <v>6816961</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5479,19 +5164,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119150306</v>
+        <v>119150294</v>
       </c>
       <c r="B48" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5519,10 +5199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486016</v>
+        <v>485958</v>
       </c>
       <c r="R48" t="n">
-        <v>6816998</v>
+        <v>6816951</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5581,19 +5261,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119150339</v>
+        <v>119150296</v>
       </c>
       <c r="B49" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5621,10 +5296,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486086</v>
+        <v>485967</v>
       </c>
       <c r="R49" t="n">
-        <v>6817313</v>
+        <v>6816956</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5683,19 +5358,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119150325</v>
+        <v>119150297</v>
       </c>
       <c r="B50" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5723,10 +5393,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486153</v>
+        <v>485982</v>
       </c>
       <c r="R50" t="n">
-        <v>6817199</v>
+        <v>6816974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5785,19 +5455,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119150297</v>
+        <v>119150298</v>
       </c>
       <c r="B51" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5825,10 +5490,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485982</v>
+        <v>485992</v>
       </c>
       <c r="R51" t="n">
-        <v>6816974</v>
+        <v>6816971</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5887,19 +5552,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119150331</v>
+        <v>119150299</v>
       </c>
       <c r="B52" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5927,10 +5587,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486151</v>
+        <v>486029</v>
       </c>
       <c r="R52" t="n">
-        <v>6817248</v>
+        <v>6816933</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5989,37 +5649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119150241</v>
+        <v>119150301</v>
       </c>
       <c r="B53" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6029,10 +5684,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486273</v>
+        <v>486047</v>
       </c>
       <c r="R53" t="n">
-        <v>6817148</v>
+        <v>6816930</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6091,37 +5746,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119150360</v>
+        <v>119150302</v>
       </c>
       <c r="B54" t="n">
-        <v>78169</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6131,10 +5781,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485968</v>
+        <v>486049</v>
       </c>
       <c r="R54" t="n">
-        <v>6817191</v>
+        <v>6816936</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6193,37 +5843,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119150359</v>
+        <v>119150303</v>
       </c>
       <c r="B55" t="n">
-        <v>78169</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6233,10 +5878,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485978</v>
+        <v>486048</v>
       </c>
       <c r="R55" t="n">
-        <v>6817236</v>
+        <v>6816957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6295,19 +5940,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119150323</v>
+        <v>119150304</v>
       </c>
       <c r="B56" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6335,10 +5975,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486228</v>
+        <v>486044</v>
       </c>
       <c r="R56" t="n">
-        <v>6817192</v>
+        <v>6816955</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6397,19 +6037,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119150337</v>
+        <v>119150305</v>
       </c>
       <c r="B57" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6437,10 +6072,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486111</v>
+        <v>486016</v>
       </c>
       <c r="R57" t="n">
-        <v>6817303</v>
+        <v>6816990</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6499,19 +6134,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119150280</v>
+        <v>119150306</v>
       </c>
       <c r="B58" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6539,10 +6169,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485993</v>
+        <v>486016</v>
       </c>
       <c r="R58" t="n">
-        <v>6817274</v>
+        <v>6816998</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6601,19 +6231,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119150282</v>
+        <v>119150307</v>
       </c>
       <c r="B59" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6641,10 +6266,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486007</v>
+        <v>486026</v>
       </c>
       <c r="R59" t="n">
-        <v>6817254</v>
+        <v>6817016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6703,19 +6328,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119150310</v>
+        <v>119150308</v>
       </c>
       <c r="B60" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6743,10 +6363,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486021</v>
+        <v>486025</v>
       </c>
       <c r="R60" t="n">
-        <v>6817092</v>
+        <v>6817022</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6805,19 +6425,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119150284</v>
+        <v>119150309</v>
       </c>
       <c r="B61" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6845,10 +6460,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485994</v>
+        <v>486038</v>
       </c>
       <c r="R61" t="n">
-        <v>6817252</v>
+        <v>6817021</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6907,19 +6522,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119150334</v>
+        <v>119150310</v>
       </c>
       <c r="B62" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6947,10 +6557,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486125</v>
+        <v>486021</v>
       </c>
       <c r="R62" t="n">
-        <v>6817270</v>
+        <v>6817092</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7009,37 +6619,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119150211</v>
+        <v>119150311</v>
       </c>
       <c r="B63" t="n">
-        <v>91461</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7049,10 +6654,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486007</v>
+        <v>486018</v>
       </c>
       <c r="R63" t="n">
-        <v>6817113</v>
+        <v>6817110</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7111,19 +6716,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119150294</v>
+        <v>119150312</v>
       </c>
       <c r="B64" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7151,10 +6751,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485958</v>
+        <v>486023</v>
       </c>
       <c r="R64" t="n">
-        <v>6816951</v>
+        <v>6817107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7213,19 +6813,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119150335</v>
+        <v>119150313</v>
       </c>
       <c r="B65" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7253,10 +6848,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>486124</v>
+        <v>486048</v>
       </c>
       <c r="R65" t="n">
-        <v>6817289</v>
+        <v>6817099</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7315,19 +6910,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119150352</v>
+        <v>119150314</v>
       </c>
       <c r="B66" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7355,10 +6945,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486016</v>
+        <v>486034</v>
       </c>
       <c r="R66" t="n">
-        <v>6817366</v>
+        <v>6817104</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7417,37 +7007,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119150213</v>
+        <v>119150315</v>
       </c>
       <c r="B67" t="n">
-        <v>91492</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7457,10 +7042,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>486259</v>
+        <v>486033</v>
       </c>
       <c r="R67" t="n">
-        <v>6817166</v>
+        <v>6817119</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7519,15 +7104,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119150258</v>
+        <v>119150316</v>
       </c>
       <c r="B68" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7535,43 +7115,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>486116</v>
+        <v>486041</v>
       </c>
       <c r="R68" t="n">
-        <v>6817190</v>
+        <v>6817122</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7630,37 +7201,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119150206</v>
+        <v>119150317</v>
       </c>
       <c r="B69" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7670,10 +7236,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486072</v>
+        <v>486048</v>
       </c>
       <c r="R69" t="n">
-        <v>6817320</v>
+        <v>6817142</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7732,19 +7298,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119150324</v>
+        <v>119150318</v>
       </c>
       <c r="B70" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7772,10 +7333,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486198</v>
+        <v>486074</v>
       </c>
       <c r="R70" t="n">
-        <v>6817181</v>
+        <v>6817180</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7834,19 +7395,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119150286</v>
+        <v>119150319</v>
       </c>
       <c r="B71" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7874,10 +7430,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485981</v>
+        <v>486195</v>
       </c>
       <c r="R71" t="n">
-        <v>6817231</v>
+        <v>6817154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7936,19 +7492,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119150296</v>
+        <v>119150320</v>
       </c>
       <c r="B72" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7976,10 +7527,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485967</v>
+        <v>486279</v>
       </c>
       <c r="R72" t="n">
-        <v>6816956</v>
+        <v>6817148</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8038,37 +7589,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119150203</v>
+        <v>119150322</v>
       </c>
       <c r="B73" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8078,10 +7624,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486021</v>
+        <v>486264</v>
       </c>
       <c r="R73" t="n">
-        <v>6817092</v>
+        <v>6817132</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8140,37 +7686,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119150243</v>
+        <v>119150323</v>
       </c>
       <c r="B74" t="n">
-        <v>93933</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8180,10 +7721,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486026</v>
+        <v>486228</v>
       </c>
       <c r="R74" t="n">
-        <v>6816986</v>
+        <v>6817192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8242,59 +7783,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119150358</v>
+        <v>119150324</v>
       </c>
       <c r="B75" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486031</v>
+        <v>486198</v>
       </c>
       <c r="R75" t="n">
-        <v>6817090</v>
+        <v>6817181</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8353,19 +7880,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119150309</v>
+        <v>119150325</v>
       </c>
       <c r="B76" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8393,10 +7915,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486038</v>
+        <v>486153</v>
       </c>
       <c r="R76" t="n">
-        <v>6817021</v>
+        <v>6817199</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8455,19 +7977,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119150354</v>
+        <v>119150326</v>
       </c>
       <c r="B77" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8495,10 +8012,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485992</v>
+        <v>486175</v>
       </c>
       <c r="R77" t="n">
-        <v>6817380</v>
+        <v>6817202</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8557,19 +8074,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119150293</v>
+        <v>119150327</v>
       </c>
       <c r="B78" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8597,10 +8109,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485956</v>
+        <v>486173</v>
       </c>
       <c r="R78" t="n">
-        <v>6816961</v>
+        <v>6817207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8659,37 +8171,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119150191</v>
+        <v>119150328</v>
       </c>
       <c r="B79" t="n">
-        <v>74636</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8699,10 +8206,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>485995</v>
+        <v>486177</v>
       </c>
       <c r="R79" t="n">
-        <v>6817369</v>
+        <v>6817210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8761,37 +8268,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119150232</v>
+        <v>119150329</v>
       </c>
       <c r="B80" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8801,10 +8303,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>485981</v>
+        <v>486162</v>
       </c>
       <c r="R80" t="n">
-        <v>6817070</v>
+        <v>6817235</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8863,37 +8365,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119150240</v>
+        <v>119150331</v>
       </c>
       <c r="B81" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8903,10 +8400,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>485982</v>
+        <v>486151</v>
       </c>
       <c r="R81" t="n">
-        <v>6817069</v>
+        <v>6817248</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8965,15 +8462,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119150245</v>
+        <v>119150332</v>
       </c>
       <c r="B82" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8981,21 +8473,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9005,10 +8497,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486108</v>
+        <v>486120</v>
       </c>
       <c r="R82" t="n">
-        <v>6817181</v>
+        <v>6817245</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9041,11 +8533,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9072,15 +8559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119150248</v>
+        <v>119150333</v>
       </c>
       <c r="B83" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9088,43 +8570,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486126</v>
+        <v>486124</v>
       </c>
       <c r="R83" t="n">
-        <v>6817176</v>
+        <v>6817261</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9183,37 +8656,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119150195</v>
+        <v>119150334</v>
       </c>
       <c r="B84" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9223,10 +8691,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485994</v>
+        <v>486125</v>
       </c>
       <c r="R84" t="n">
-        <v>6817274</v>
+        <v>6817270</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9285,15 +8753,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119150264</v>
+        <v>119150335</v>
       </c>
       <c r="B85" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9301,43 +8764,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486005</v>
+        <v>486124</v>
       </c>
       <c r="R85" t="n">
-        <v>6816970</v>
+        <v>6817289</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9396,19 +8850,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119150314</v>
+        <v>119150336</v>
       </c>
       <c r="B86" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -9436,10 +8885,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486034</v>
+        <v>486126</v>
       </c>
       <c r="R86" t="n">
-        <v>6817104</v>
+        <v>6817300</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9498,19 +8947,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119150319</v>
+        <v>119150337</v>
       </c>
       <c r="B87" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -9538,10 +8982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486195</v>
+        <v>486111</v>
       </c>
       <c r="R87" t="n">
-        <v>6817154</v>
+        <v>6817303</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9600,19 +9044,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119150288</v>
+        <v>119150338</v>
       </c>
       <c r="B88" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -9640,10 +9079,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485994</v>
+        <v>486090</v>
       </c>
       <c r="R88" t="n">
-        <v>6817085</v>
+        <v>6817306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9702,19 +9141,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119150329</v>
+        <v>119150339</v>
       </c>
       <c r="B89" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -9742,10 +9176,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486162</v>
+        <v>486086</v>
       </c>
       <c r="R89" t="n">
-        <v>6817235</v>
+        <v>6817313</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9804,37 +9238,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119150230</v>
+        <v>119150340</v>
       </c>
       <c r="B90" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9844,10 +9273,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486062</v>
+        <v>486083</v>
       </c>
       <c r="R90" t="n">
-        <v>6817142</v>
+        <v>6817320</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9906,15 +9335,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119150249</v>
+        <v>119150341</v>
       </c>
       <c r="B91" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9922,43 +9346,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486181</v>
+        <v>486116</v>
       </c>
       <c r="R91" t="n">
-        <v>6817184</v>
+        <v>6817329</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10017,59 +9432,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119150220</v>
+        <v>119150342</v>
       </c>
       <c r="B92" t="n">
-        <v>97926</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486025</v>
+        <v>486119</v>
       </c>
       <c r="R92" t="n">
-        <v>6816972</v>
+        <v>6817359</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10128,19 +9529,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119150345</v>
+        <v>119150343</v>
       </c>
       <c r="B93" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -10168,10 +9564,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486086</v>
+        <v>486120</v>
       </c>
       <c r="R93" t="n">
-        <v>6817374</v>
+        <v>6817370</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10230,37 +9626,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119150214</v>
+        <v>119150344</v>
       </c>
       <c r="B94" t="n">
-        <v>91492</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10270,7 +9661,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485994</v>
+        <v>486113</v>
       </c>
       <c r="R94" t="n">
         <v>6817373</v>
@@ -10332,15 +9723,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119150246</v>
+        <v>119150345</v>
       </c>
       <c r="B95" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10348,43 +9734,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>485894</v>
+        <v>486086</v>
       </c>
       <c r="R95" t="n">
-        <v>6816982</v>
+        <v>6817374</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10443,37 +9820,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119150225</v>
+        <v>119150346</v>
       </c>
       <c r="B96" t="n">
-        <v>96860</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10483,10 +9855,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486122</v>
+        <v>486090</v>
       </c>
       <c r="R96" t="n">
-        <v>6817260</v>
+        <v>6817342</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10545,19 +9917,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119150340</v>
+        <v>119150347</v>
       </c>
       <c r="B97" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -10585,10 +9952,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>486083</v>
+        <v>486061</v>
       </c>
       <c r="R97" t="n">
-        <v>6817320</v>
+        <v>6817331</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10647,37 +10014,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119150234</v>
+        <v>119150348</v>
       </c>
       <c r="B98" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10687,10 +10049,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485960</v>
+        <v>486055</v>
       </c>
       <c r="R98" t="n">
-        <v>6817024</v>
+        <v>6817334</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10749,15 +10111,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119150257</v>
+        <v>119150349</v>
       </c>
       <c r="B99" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10765,41 +10122,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>486011</v>
+        <v>486057</v>
       </c>
       <c r="R99" t="n">
-        <v>6816968</v>
+        <v>6817342</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10834,18 +10184,12 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10864,59 +10208,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119150219</v>
+        <v>119150350</v>
       </c>
       <c r="B100" t="n">
-        <v>97926</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>486025</v>
+        <v>486051</v>
       </c>
       <c r="R100" t="n">
-        <v>6816965</v>
+        <v>6817353</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10975,37 +10305,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119150196</v>
+        <v>119150351</v>
       </c>
       <c r="B101" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11015,10 +10340,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485978</v>
+        <v>486038</v>
       </c>
       <c r="R101" t="n">
-        <v>6817240</v>
+        <v>6817373</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11077,37 +10402,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119150205</v>
+        <v>119150352</v>
       </c>
       <c r="B102" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11117,10 +10437,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486049</v>
+        <v>486016</v>
       </c>
       <c r="R102" t="n">
-        <v>6817096</v>
+        <v>6817366</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11179,19 +10499,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119150317</v>
+        <v>119150353</v>
       </c>
       <c r="B103" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -11219,10 +10534,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486048</v>
+        <v>486009</v>
       </c>
       <c r="R103" t="n">
-        <v>6817142</v>
+        <v>6817379</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11281,19 +10596,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119150318</v>
+        <v>119150354</v>
       </c>
       <c r="B104" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -11321,10 +10631,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486074</v>
+        <v>485992</v>
       </c>
       <c r="R104" t="n">
-        <v>6817180</v>
+        <v>6817380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11383,19 +10693,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119150328</v>
+        <v>119150355</v>
       </c>
       <c r="B105" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -11423,10 +10728,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486177</v>
+        <v>485999</v>
       </c>
       <c r="R105" t="n">
-        <v>6817210</v>
+        <v>6817372</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11485,19 +10790,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119150303</v>
+        <v>119150356</v>
       </c>
       <c r="B106" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -11525,10 +10825,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>486048</v>
+        <v>485987</v>
       </c>
       <c r="R106" t="n">
-        <v>6816957</v>
+        <v>6817330</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11587,19 +10887,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119150313</v>
+        <v>119150357</v>
       </c>
       <c r="B107" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -11627,10 +10922,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>486048</v>
+        <v>485990</v>
       </c>
       <c r="R107" t="n">
-        <v>6817099</v>
+        <v>6817323</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11689,15 +10984,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119150346</v>
+        <v>119150189</v>
       </c>
       <c r="B108" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11705,21 +10995,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11729,10 +11019,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>486090</v>
+        <v>485979</v>
       </c>
       <c r="R108" t="n">
-        <v>6817342</v>
+        <v>6816957</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11791,15 +11081,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119150233</v>
+        <v>119150191</v>
       </c>
       <c r="B109" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11807,21 +11092,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11831,10 +11116,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485984</v>
+        <v>485995</v>
       </c>
       <c r="R109" t="n">
-        <v>6817035</v>
+        <v>6817369</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11893,59 +11178,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119150271</v>
+        <v>119150192</v>
       </c>
       <c r="B110" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>486075</v>
+        <v>485980</v>
       </c>
       <c r="R110" t="n">
-        <v>6817321</v>
+        <v>6817365</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12004,59 +11275,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119150268</v>
+        <v>119150193</v>
       </c>
       <c r="B111" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485903</v>
+        <v>485986</v>
       </c>
       <c r="R111" t="n">
-        <v>6816985</v>
+        <v>6817328</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12115,15 +11372,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119150207</v>
+        <v>119150232</v>
       </c>
       <c r="B112" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12131,21 +11383,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12155,10 +11407,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>486080</v>
+        <v>485981</v>
       </c>
       <c r="R112" t="n">
-        <v>6817326</v>
+        <v>6817070</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12217,15 +11469,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119150197</v>
+        <v>119150233</v>
       </c>
       <c r="B113" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12233,21 +11480,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12257,10 +11504,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>486004</v>
+        <v>485984</v>
       </c>
       <c r="R113" t="n">
-        <v>6817124</v>
+        <v>6817035</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12319,15 +11566,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119150215</v>
+        <v>119150234</v>
       </c>
       <c r="B114" t="n">
-        <v>91882</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12335,21 +11577,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12359,10 +11601,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>486037</v>
+        <v>485960</v>
       </c>
       <c r="R114" t="n">
-        <v>6817106</v>
+        <v>6817024</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12421,15 +11663,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119150355</v>
+        <v>119150235</v>
       </c>
       <c r="B115" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12437,21 +11674,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12461,10 +11698,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485999</v>
+        <v>485963</v>
       </c>
       <c r="R115" t="n">
-        <v>6817372</v>
+        <v>6817028</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12523,15 +11760,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119150326</v>
+        <v>119150236</v>
       </c>
       <c r="B116" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12539,21 +11771,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12563,10 +11795,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>486175</v>
+        <v>486274</v>
       </c>
       <c r="R116" t="n">
-        <v>6817202</v>
+        <v>6817146</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12625,59 +11857,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119150247</v>
+        <v>119150237</v>
       </c>
       <c r="B117" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>486041</v>
+        <v>486273</v>
       </c>
       <c r="R117" t="n">
-        <v>6817122</v>
+        <v>6817146</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12736,59 +11954,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119150265</v>
+        <v>119150216</v>
       </c>
       <c r="B118" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>486031</v>
+        <v>486010</v>
       </c>
       <c r="R118" t="n">
-        <v>6816959</v>
+        <v>6817122</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12847,59 +12051,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119150250</v>
+        <v>119150217</v>
       </c>
       <c r="B119" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>486162</v>
+        <v>485996</v>
       </c>
       <c r="R119" t="n">
-        <v>6817236</v>
+        <v>6817083</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12958,66 +12148,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119150263</v>
+        <v>119150240</v>
       </c>
       <c r="B120" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485997</v>
+        <v>485982</v>
       </c>
       <c r="R120" t="n">
-        <v>6816970</v>
+        <v>6817069</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13052,18 +12221,12 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13082,37 +12245,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119150348</v>
+        <v>119150241</v>
       </c>
       <c r="B121" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13122,10 +12280,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>486055</v>
+        <v>486273</v>
       </c>
       <c r="R121" t="n">
-        <v>6817334</v>
+        <v>6817148</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13184,50 +12342,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119150298</v>
+        <v>119150222</v>
       </c>
       <c r="B122" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485992</v>
+        <v>486130</v>
       </c>
       <c r="R122" t="n">
-        <v>6816971</v>
+        <v>6817297</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13286,15 +12444,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119150290</v>
+        <v>119150209</v>
       </c>
       <c r="B123" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13302,34 +12455,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485975</v>
+        <v>485983</v>
       </c>
       <c r="R123" t="n">
-        <v>6817009</v>
+        <v>6817364</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13388,15 +12546,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119150361</v>
+        <v>119150210</v>
       </c>
       <c r="B124" t="n">
-        <v>78169</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13404,21 +12557,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13428,10 +12581,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>486064</v>
+        <v>485992</v>
       </c>
       <c r="R124" t="n">
-        <v>6817046</v>
+        <v>6817278</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13490,37 +12643,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119150307</v>
+        <v>119150245</v>
       </c>
       <c r="B125" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13530,10 +12678,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>486026</v>
+        <v>486108</v>
       </c>
       <c r="R125" t="n">
-        <v>6817016</v>
+        <v>6817181</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13566,6 +12714,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13592,50 +12745,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119150289</v>
+        <v>119150246</v>
       </c>
       <c r="B126" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485978</v>
+        <v>485894</v>
       </c>
       <c r="R126" t="n">
-        <v>6817031</v>
+        <v>6816982</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13694,50 +12851,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119150212</v>
+        <v>119150247</v>
       </c>
       <c r="B127" t="n">
-        <v>90065</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>486061</v>
+        <v>486041</v>
       </c>
       <c r="R127" t="n">
-        <v>6817039</v>
+        <v>6817122</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13796,15 +12957,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119150260</v>
+        <v>119150248</v>
       </c>
       <c r="B128" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13831,7 +12987,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -13845,10 +13001,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>486071</v>
+        <v>486126</v>
       </c>
       <c r="R128" t="n">
-        <v>6817329</v>
+        <v>6817176</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13907,15 +13063,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119150256</v>
+        <v>119150249</v>
       </c>
       <c r="B129" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13942,7 +13093,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -13956,10 +13107,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>486104</v>
+        <v>486181</v>
       </c>
       <c r="R129" t="n">
-        <v>6817187</v>
+        <v>6817184</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14018,50 +13169,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119150226</v>
+        <v>119150250</v>
       </c>
       <c r="B130" t="n">
-        <v>96866</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>486082</v>
+        <v>486162</v>
       </c>
       <c r="R130" t="n">
-        <v>6817192</v>
+        <v>6817236</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14094,11 +13249,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14125,48 +13275,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119150242</v>
+        <v>119150251</v>
       </c>
       <c r="B131" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Difslovatjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>486067</v>
+        <v>486127</v>
       </c>
       <c r="R131" t="n">
-        <v>6817036</v>
+        <v>6817270</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14201,18 +13357,12 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14228,6 +13378,2748 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>119150252</v>
+      </c>
+      <c r="B132" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>486019</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6816965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>119150253</v>
+      </c>
+      <c r="B133" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>486122</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6817177</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>119150254</v>
+      </c>
+      <c r="B134" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>486174</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6817201</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>119150255</v>
+      </c>
+      <c r="B135" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>486011</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6816968</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>119150256</v>
+      </c>
+      <c r="B136" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>486104</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6817187</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>119150258</v>
+      </c>
+      <c r="B137" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>486116</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6817190</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>119150260</v>
+      </c>
+      <c r="B138" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>486071</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6817329</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>119150261</v>
+      </c>
+      <c r="B139" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>486161</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6817238</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>119150262</v>
+      </c>
+      <c r="B140" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>486232</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6817200</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>119150263</v>
+      </c>
+      <c r="B141" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>485997</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6816970</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>119150264</v>
+      </c>
+      <c r="B142" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>486005</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6816970</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>119150265</v>
+      </c>
+      <c r="B143" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>486031</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6816959</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>119150266</v>
+      </c>
+      <c r="B144" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>486120</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6817186</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>119150267</v>
+      </c>
+      <c r="B145" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>485912</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6816984</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>119150268</v>
+      </c>
+      <c r="B146" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>485903</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6816985</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>119150269</v>
+      </c>
+      <c r="B147" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>486231</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6817154</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>119150271</v>
+      </c>
+      <c r="B148" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>486075</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6817321</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>119150226</v>
+      </c>
+      <c r="B149" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>486082</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6817192</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>119150225</v>
+      </c>
+      <c r="B150" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>486122</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6817260</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>119150218</v>
+      </c>
+      <c r="B151" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>486005</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6816970</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>119150219</v>
+      </c>
+      <c r="B152" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>486025</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6816965</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>119150220</v>
+      </c>
+      <c r="B153" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>486025</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6816972</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>119150221</v>
+      </c>
+      <c r="B154" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>485997</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6816970</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>119150230</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>486062</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6817142</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>119150212</v>
+      </c>
+      <c r="B156" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>486061</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6817039</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>119150242</v>
+      </c>
+      <c r="B157" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Difslovatjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>486067</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6817036</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51902-2023 artfynd.xlsx
+++ b/artfynd/A 51902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY157"/>
+  <dimension ref="A1:AZ157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150194</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150198</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150199</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150202</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150203</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150204</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150205</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150206</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150207</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150208</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150359</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150360</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150361</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150231</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150223</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150224</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150243</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150228</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3124,6 +3249,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150358</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150211</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150213</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3415,6 +3555,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150214</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3512,6 +3657,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150276</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3609,6 +3759,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150277</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3706,6 +3861,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150278</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3803,6 +3963,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150279</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3900,6 +4065,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150280</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3997,6 +4167,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150281</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4094,6 +4269,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150282</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4191,6 +4371,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150283</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4288,6 +4473,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150284</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4385,6 +4575,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150285</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4482,6 +4677,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150286</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4579,6 +4779,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150287</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4676,6 +4881,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150288</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4773,6 +4983,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150289</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4870,6 +5085,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150290</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4967,6 +5187,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150291</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5064,6 +5289,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150292</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5161,6 +5391,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150293</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5258,6 +5493,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150294</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5355,6 +5595,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150296</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5452,6 +5697,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150297</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5549,6 +5799,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150298</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5646,6 +5901,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150299</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5743,6 +6003,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150301</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5840,6 +6105,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150302</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5937,6 +6207,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150303</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6034,6 +6309,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150304</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6131,6 +6411,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150305</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6228,6 +6513,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150306</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6325,6 +6615,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150307</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6422,6 +6717,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150308</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6519,6 +6819,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150309</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6616,6 +6921,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150310</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6713,6 +7023,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150311</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6810,6 +7125,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150312</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6907,6 +7227,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150313</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7004,6 +7329,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150314</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7101,6 +7431,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150315</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7198,6 +7533,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150316</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7295,6 +7635,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150317</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7392,6 +7737,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150318</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7489,6 +7839,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150319</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7586,6 +7941,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150320</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7683,6 +8043,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150322</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7780,6 +8145,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150323</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7877,6 +8247,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150324</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7974,6 +8349,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150325</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8071,6 +8451,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150326</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8168,6 +8553,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150327</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8265,6 +8655,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150328</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8362,6 +8757,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150329</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8459,6 +8859,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150331</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8556,6 +8961,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150332</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8653,6 +9063,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150333</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8750,6 +9165,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150334</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8847,6 +9267,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150335</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8944,6 +9369,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150336</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9041,6 +9471,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150337</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9138,6 +9573,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150338</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9235,6 +9675,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150339</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9332,6 +9777,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150340</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9429,6 +9879,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150341</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9526,6 +9981,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150342</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9623,6 +10083,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150343</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9720,6 +10185,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150344</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9817,6 +10287,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150345</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9914,6 +10389,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150346</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10011,6 +10491,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150347</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10108,6 +10593,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150348</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10205,6 +10695,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150349</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10302,6 +10797,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150350</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10399,6 +10899,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150351</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10496,6 +11001,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150352</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10593,6 +11103,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150353</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10690,6 +11205,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150354</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10787,6 +11307,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150355</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10884,6 +11409,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150356</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10981,6 +11511,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150357</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11078,6 +11613,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150189</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11175,6 +11715,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150191</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11272,6 +11817,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150192</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11369,6 +11919,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150193</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11466,6 +12021,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150232</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11563,6 +12123,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150233</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11660,6 +12225,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150234</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11757,6 +12327,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150235</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11854,6 +12429,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150236</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11951,6 +12531,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150237</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12048,6 +12633,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150216</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12145,6 +12735,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150217</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12242,6 +12837,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150240</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12339,6 +12939,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150241</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12441,6 +13046,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150222</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12543,6 +13153,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150209</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12640,6 +13255,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150210</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12742,6 +13362,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150245</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12848,6 +13473,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150246</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12954,6 +13584,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150247</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13060,6 +13695,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150248</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13166,6 +13806,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150249</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13272,6 +13917,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150250</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13378,6 +14028,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150251</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13484,6 +14139,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150252</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13590,6 +14250,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150253</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13696,6 +14361,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150254</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13802,6 +14472,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150255</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13908,6 +14583,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150256</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14014,6 +14694,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150258</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14120,6 +14805,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150260</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14226,6 +14916,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150261</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14345,6 +15040,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150262</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14464,6 +15164,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150263</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14570,6 +15275,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150264</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14676,6 +15386,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150265</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14782,6 +15497,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150266</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14888,6 +15608,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150267</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14994,6 +15719,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150268</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15100,6 +15830,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150269</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15206,6 +15941,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150271</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15308,6 +16048,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150226</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15405,6 +16150,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150225</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15511,6 +16261,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150218</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15617,6 +16372,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150219</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15723,6 +16483,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150220</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15820,6 +16585,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150221</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15917,6 +16687,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150230</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16014,6 +16789,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150212</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16120,8 +16900,171 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119150242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>